--- a/output/daily_ratings/uk_ratings_2026-04-21.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-04-21.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P123"/>
+  <dimension ref="A1:P179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1718,17 +1718,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sunriseontheboyne (IRE)</t>
+          <t>Antrim</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="K22" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Antrim</t>
+          <t>Romieu</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K23" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Romieu</t>
+          <t>Sunriseontheboyne (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Wish This</t>
+          <t>No Return (IRE)</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K33" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
@@ -2420,17 +2420,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>No Return (IRE)</t>
+          <t>Wish This</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K34" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lion City (IRE)</t>
+          <t>Capone (GER)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K44" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Different Drum</t>
+          <t>Charlie Darling (FR)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K45" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Capone (GER)</t>
+          <t>Home And Dry (IRE)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K46" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
@@ -3178,17 +3178,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Charlie Darling (FR)</t>
+          <t>Lion City (IRE)</t>
         </is>
       </c>
       <c r="I47" t="n">
         <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="K47" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Home And Dry (IRE)</t>
+          <t>Different Drum</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K48" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
@@ -3708,17 +3708,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Speeding Bullet (IRE)</t>
+          <t>Tanjen (IRE)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K56" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tanjen (IRE)</t>
+          <t>Fillys Last Lady</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="K57" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fillys Last Lady</t>
+          <t>Komorkis (IRE)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K58" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Komorkis (IRE)</t>
+          <t>Midnight Lir (IRE)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K59" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
@@ -3932,17 +3932,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Midnight Lir (IRE)</t>
+          <t>Speeding Bullet (IRE)</t>
         </is>
       </c>
       <c r="I60" t="n">
         <v>5</v>
       </c>
       <c r="J60" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K60" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
@@ -4319,23 +4319,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>6.013636363636364</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Siouxperb</t>
+          <t>Final Appeal (IRE)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4360,10 +4360,10 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>71.47</v>
+        <v>61.69</v>
       </c>
       <c r="N67" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4377,23 +4377,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>6.013636363636364</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ogorman</t>
+          <t>Noble Raider (IRE)</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4417,13 +4417,13 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="M68" t="n">
-        <v>71.47</v>
+        <v>61.69</v>
       </c>
       <c r="N68" t="n">
-        <v>58.8</v>
+        <v>56.4</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4437,23 +4437,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>6.013636363636364</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Priscillas Hope</t>
+          <t>Blackberry Bold</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4477,13 +4477,13 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="M69" t="n">
-        <v>71.47</v>
+        <v>61.69</v>
       </c>
       <c r="N69" t="n">
-        <v>44.3</v>
+        <v>32.5</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4497,23 +4497,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>6.013636363636364</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Viking Barbie (IRE)</t>
+          <t>Magical Life</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4537,13 +4537,13 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>9.75</v>
+        <v>11.25</v>
       </c>
       <c r="M70" t="n">
-        <v>71.47</v>
+        <v>61.69</v>
       </c>
       <c r="N70" t="n">
-        <v>38.5</v>
+        <v>21.1</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4557,23 +4557,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>6.013636363636364</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -4584,26 +4584,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Hamdani Mokhater</t>
+          <t>Marralyn (IRE)</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>12.25</v>
+        <v>14.75</v>
       </c>
       <c r="M71" t="n">
-        <v>71.47</v>
+        <v>61.69</v>
       </c>
       <c r="N71" t="n">
-        <v>32.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4617,57 +4617,55 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>12.23181818181818</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" t="n">
         <v>1</v>
       </c>
-      <c r="C72" t="n">
-        <v>6.013636363636364</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Good To Firm</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>4</v>
-      </c>
-      <c r="G72" t="n">
-        <v>6</v>
-      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Taseem</t>
+          <t>Forever Perfect</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>20.25</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>71.47</v>
+        <v>163.78</v>
       </c>
       <c r="N72" t="n">
-        <v>19.2</v>
+        <v>30.7</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -4677,107 +4675,113 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>11.47272727272727</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Close To Me</t>
+          <t>Crown Inn To Win (IRE)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M73" t="n">
-        <v>141.08</v>
-      </c>
-      <c r="N73" t="inlineStr"/>
+        <v>163.78</v>
+      </c>
+      <c r="N73" t="n">
+        <v>30.6</v>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>11.47272727272727</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Brilliant Star</t>
+          <t>Itsonlyrockandroll</t>
         </is>
       </c>
       <c r="I74" t="n">
         <v>3</v>
       </c>
       <c r="J74" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M74" t="n">
-        <v>141.08</v>
+        <v>163.78</v>
       </c>
       <c r="N74" t="n">
-        <v>77.8</v>
+        <v>29.6</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4791,53 +4795,53 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>11.47272727272727</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fanciulla Del West</t>
+          <t>Steel Fixer</t>
         </is>
       </c>
       <c r="I75" t="n">
         <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L75" t="n">
-        <v>10</v>
+        <v>5.25</v>
       </c>
       <c r="M75" t="n">
-        <v>141.08</v>
+        <v>163.78</v>
       </c>
       <c r="N75" t="n">
-        <v>58.6</v>
+        <v>23.1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4851,53 +4855,53 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>11.47272727272727</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kenkelly (IRE)</t>
+          <t>Moon Is Up (IRE)</t>
         </is>
       </c>
       <c r="I76" t="n">
         <v>3</v>
       </c>
       <c r="J76" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L76" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="M76" t="n">
-        <v>141.08</v>
+        <v>163.78</v>
       </c>
       <c r="N76" t="n">
-        <v>42.2</v>
+        <v>19.7</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -4911,53 +4915,53 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>11.47272727272727</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Clarissa Eclipse</t>
+          <t>Corduroy</t>
         </is>
       </c>
       <c r="I77" t="n">
         <v>3</v>
       </c>
       <c r="J77" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L77" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="M77" t="n">
-        <v>141.08</v>
+        <v>163.78</v>
       </c>
       <c r="N77" t="n">
-        <v>17.3</v>
+        <v>-15.2</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -4971,57 +4975,55 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>11.47272727272727</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Millies A Minx</t>
+          <t>Em Four</t>
         </is>
       </c>
       <c r="I78" t="n">
         <v>4</v>
       </c>
       <c r="J78" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>91.5</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>141.08</v>
+        <v>60.85</v>
       </c>
       <c r="N78" t="n">
-        <v>-30.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -5031,51 +5033,53 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>10.10454545454546</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Room Fourteen</t>
+          <t>Shalaa Asker</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J79" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K79" t="n">
-        <v>66</v>
-      </c>
-      <c r="L79" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M79" t="n">
-        <v>125.27</v>
+        <v>60.85</v>
       </c>
       <c r="N79" t="n">
-        <v>77.8</v>
+        <v>56.9</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5089,53 +5093,53 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>10.10454545454546</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>King Of Berkshire (IRE)</t>
+          <t>Binadham (IRE)</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K80" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L80" t="n">
-        <v>0.05</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>125.27</v>
+        <v>60.85</v>
       </c>
       <c r="N80" t="n">
-        <v>78.8</v>
+        <v>61.9</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5149,53 +5153,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>10.10454545454546</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Crimson Rambler</t>
+          <t>Midnight Call (IRE)</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K81" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L81" t="n">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="M81" t="n">
-        <v>125.27</v>
+        <v>60.85</v>
       </c>
       <c r="N81" t="n">
-        <v>72.8</v>
+        <v>45.4</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5209,53 +5213,53 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>10.10454545454546</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Boilermaker (FR)</t>
+          <t>Phoenix Beach (IRE)</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="K82" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L82" t="n">
-        <v>5.3</v>
+        <v>6.35</v>
       </c>
       <c r="M82" t="n">
-        <v>125.27</v>
+        <v>60.85</v>
       </c>
       <c r="N82" t="n">
-        <v>63.4</v>
+        <v>33.9</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5263,59 +5267,59 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>10.10454545454546</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Heated Moment</t>
+          <t>Diomed Spirit</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K83" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L83" t="n">
-        <v>8.050000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M83" t="n">
-        <v>125.27</v>
+        <v>60.85</v>
       </c>
       <c r="N83" t="n">
-        <v>53.5</v>
+        <v>39.3</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5323,59 +5327,59 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>10.10454545454546</v>
+        <v>5.095454545454546</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Joyful Lawyer (USA)</t>
+          <t>Smooth Silesie (IRE)</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K84" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="L84" t="n">
-        <v>8.15</v>
+        <v>8.25</v>
       </c>
       <c r="M84" t="n">
-        <v>125.27</v>
+        <v>60.85</v>
       </c>
       <c r="N84" t="n">
-        <v>61.6</v>
+        <v>38.6</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5389,113 +5393,107 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>10.10454545454546</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kokushoku (IRE)</t>
+          <t>Three Yorkshiremen (IRE)</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J85" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K85" t="n">
-        <v>66</v>
-      </c>
-      <c r="L85" t="n">
-        <v>8.18</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
-        <v>125.27</v>
-      </c>
-      <c r="N85" t="n">
-        <v>61</v>
-      </c>
+        <v>163.61</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>10.10454545454546</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Pantiles Gift</t>
+          <t>Beaune (IRE)</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K86" t="n">
-        <v>71</v>
-      </c>
-      <c r="L86" t="n">
-        <v>11.68</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>125.27</v>
+        <v>163.61</v>
       </c>
       <c r="N86" t="n">
-        <v>56.3</v>
+        <v>23.5</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5503,59 +5501,59 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>10.10454545454546</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Izznt She Hot</t>
+          <t>Wave Rock (IRE)</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K87" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L87" t="n">
-        <v>13.68</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>125.27</v>
+        <v>163.61</v>
       </c>
       <c r="N87" t="n">
-        <v>50.1</v>
+        <v>20</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5563,117 +5561,119 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>6.013636363636364</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>The Bay Warrior (IRE)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>135</v>
+      </c>
+      <c r="K88" t="n">
+        <v>59</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M88" t="n">
+        <v>163.61</v>
+      </c>
+      <c r="N88" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
         <v>1</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Caragio (IRE)</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>6</v>
-      </c>
-      <c r="J88" t="n">
-        <v>131</v>
-      </c>
-      <c r="K88" t="n">
-        <v>66</v>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="n">
-        <v>69.66</v>
-      </c>
-      <c r="N88" t="n">
-        <v>74</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>6.013636363636364</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Dark Side Thunder</t>
+          <t>Rubellite (IRE)</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J89" t="n">
         <v>134</v>
       </c>
       <c r="K89" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L89" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="M89" t="n">
-        <v>69.66</v>
+        <v>163.61</v>
       </c>
       <c r="N89" t="n">
-        <v>65.3</v>
+        <v>17.9</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -5687,53 +5687,53 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>6.013636363636364</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Fenlander</t>
+          <t>Knight Of Magic (IRE)</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J90" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K90" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L90" t="n">
-        <v>3.28</v>
+        <v>7.78</v>
       </c>
       <c r="M90" t="n">
-        <v>69.66</v>
+        <v>163.61</v>
       </c>
       <c r="N90" t="n">
-        <v>58.5</v>
+        <v>1.6</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -5741,59 +5741,59 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>6.013636363636364</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Ironist (IRE)</t>
+          <t>Late Claim (FR)</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K91" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="L91" t="n">
-        <v>3.43</v>
+        <v>7.83</v>
       </c>
       <c r="M91" t="n">
-        <v>69.66</v>
+        <v>163.61</v>
       </c>
       <c r="N91" t="n">
-        <v>65.09999999999999</v>
+        <v>-2.2</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5801,59 +5801,59 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>6.013636363636364</v>
+        <v>12.23181818181818</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>My Mate Kev</t>
+          <t>Phyllis Burton</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K92" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L92" t="n">
-        <v>3.58</v>
+        <v>12.33</v>
       </c>
       <c r="M92" t="n">
-        <v>69.66</v>
+        <v>163.61</v>
       </c>
       <c r="N92" t="n">
-        <v>58.7</v>
+        <v>-6.6</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -5861,59 +5861,57 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>6.013636363636364</v>
+        <v>6.090909090909091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>5</v>
       </c>
       <c r="G93" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bill Plumb (IRE)</t>
+          <t>Daytona Lady (IRE)</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
         <v>134</v>
       </c>
       <c r="K93" t="n">
-        <v>69</v>
-      </c>
-      <c r="L93" t="n">
-        <v>7.33</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
-        <v>69.66</v>
+        <v>73.36</v>
       </c>
       <c r="N93" t="n">
-        <v>52.8</v>
+        <v>71</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5921,113 +5919,119 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>6.013636363636364</v>
+        <v>6.090909090909091</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Love Alive</t>
+          <t>Tabby</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K94" t="n">
-        <v>68</v>
-      </c>
-      <c r="L94" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M94" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N94" t="inlineStr"/>
+        <v>73.36</v>
+      </c>
+      <c r="N94" t="n">
+        <v>75.59999999999999</v>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>5</v>
       </c>
       <c r="C95" t="n">
-        <v>6.013636363636364</v>
+        <v>6.090909090909091</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Space Bear (IRE)</t>
+          <t>Filly Foden (IRE)</t>
         </is>
       </c>
       <c r="I95" t="n">
         <v>3</v>
       </c>
       <c r="J95" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K95" t="n">
-        <v>70</v>
-      </c>
-      <c r="L95" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M95" t="n">
-        <v>69.55</v>
+        <v>73.36</v>
       </c>
       <c r="N95" t="n">
-        <v>83.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6041,53 +6045,53 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>5</v>
       </c>
       <c r="C96" t="n">
-        <v>6.013636363636364</v>
+        <v>6.090909090909091</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>5</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Argy Bhaji</t>
+          <t>Crystal Dagger</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K96" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L96" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="M96" t="n">
-        <v>69.55</v>
+        <v>73.36</v>
       </c>
       <c r="N96" t="n">
-        <v>75.09999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6101,53 +6105,53 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>6.013636363636364</v>
+        <v>6.090909090909091</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Eightthreeone</t>
+          <t>Star Marian</t>
         </is>
       </c>
       <c r="I97" t="n">
         <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K97" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L97" t="n">
-        <v>4.25</v>
+        <v>7.75</v>
       </c>
       <c r="M97" t="n">
-        <v>69.55</v>
+        <v>73.36</v>
       </c>
       <c r="N97" t="n">
-        <v>71.5</v>
+        <v>48</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6161,53 +6165,53 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>5</v>
       </c>
       <c r="C98" t="n">
-        <v>6.013636363636364</v>
+        <v>6.090909090909091</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>5</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Ocean Of Storms (FR)</t>
+          <t>Havana Joy</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K98" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L98" t="n">
-        <v>6.25</v>
+        <v>11.5</v>
       </c>
       <c r="M98" t="n">
-        <v>69.55</v>
+        <v>73.36</v>
       </c>
       <c r="N98" t="n">
-        <v>62.6</v>
+        <v>35.6</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6221,113 +6225,107 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" t="n">
-        <v>6.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Eyes Front (IRE)</t>
+          <t>Tomarlo</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>134</v>
       </c>
       <c r="K99" t="n">
-        <v>69</v>
-      </c>
-      <c r="L99" t="n">
-        <v>9.25</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="N99" t="n">
-        <v>57.9</v>
-      </c>
+        <v>88.55</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>6.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Angel Summer (IRE)</t>
+          <t>Faster Bee</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K100" t="n">
-        <v>62</v>
-      </c>
-      <c r="L100" t="n">
-        <v>11.75</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
-        <v>69.55</v>
+        <v>88.55</v>
       </c>
       <c r="N100" t="n">
-        <v>42</v>
+        <v>61.9</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6341,167 +6339,173 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" t="n">
-        <v>6.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bungle Bay (IRE)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
         <v>7</v>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Wild Rosie</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>3</v>
-      </c>
       <c r="J101" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K101" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L101" t="n">
-        <v>21.25</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
-        <v>69.55</v>
+        <v>88.55</v>
       </c>
       <c r="N101" t="n">
-        <v>29.5</v>
+        <v>54.1</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>6</v>
       </c>
       <c r="C102" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Dashing Dick (IRE)</t>
+          <t>Alyara</t>
         </is>
       </c>
       <c r="I102" t="n">
         <v>8</v>
       </c>
       <c r="J102" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K102" t="n">
-        <v>78</v>
-      </c>
-      <c r="L102" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2.05</v>
+      </c>
       <c r="M102" t="n">
-        <v>83.14</v>
-      </c>
-      <c r="N102" t="inlineStr"/>
+        <v>88.55</v>
+      </c>
+      <c r="N102" t="n">
+        <v>49.2</v>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>6</v>
       </c>
       <c r="C103" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Thomas Equinas</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J103" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K103" t="n">
-        <v>82</v>
-      </c>
-      <c r="L103" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="L103" t="n">
+        <v>2.1</v>
+      </c>
       <c r="M103" t="n">
-        <v>83.14</v>
+        <v>88.55</v>
       </c>
       <c r="N103" t="n">
-        <v>71.2</v>
+        <v>55.7</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6509,59 +6513,59 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Candonomore (FR)</t>
+          <t>Diligent Henry</t>
         </is>
       </c>
       <c r="I104" t="n">
         <v>5</v>
       </c>
       <c r="J104" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K104" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="L104" t="n">
-        <v>0.05</v>
+        <v>3.1</v>
       </c>
       <c r="M104" t="n">
-        <v>83.14</v>
+        <v>88.55</v>
       </c>
       <c r="N104" t="n">
-        <v>65.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6569,59 +6573,59 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>6</v>
       </c>
       <c r="C105" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Rogue Allegiance (IRE)</t>
+          <t>Sanditon (IRE)</t>
         </is>
       </c>
       <c r="I105" t="n">
         <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K105" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="L105" t="n">
-        <v>1.05</v>
+        <v>7.1</v>
       </c>
       <c r="M105" t="n">
-        <v>83.14</v>
+        <v>88.55</v>
       </c>
       <c r="N105" t="n">
-        <v>58.5</v>
+        <v>44.5</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6629,59 +6633,59 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G106" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Shimmering Spin (USA)</t>
+          <t>Port Hedland</t>
         </is>
       </c>
       <c r="I106" t="n">
         <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K106" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="L106" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="M106" t="n">
-        <v>83.14</v>
+        <v>88.55</v>
       </c>
       <c r="N106" t="n">
-        <v>58.7</v>
+        <v>35.7</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6695,53 +6699,53 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Mister Mojito (IRE)</t>
+          <t>Star Of Atlantis (IRE)</t>
         </is>
       </c>
       <c r="I107" t="n">
         <v>5</v>
       </c>
       <c r="J107" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K107" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L107" t="n">
-        <v>2.3</v>
+        <v>10.7</v>
       </c>
       <c r="M107" t="n">
-        <v>83.14</v>
+        <v>88.55</v>
       </c>
       <c r="N107" t="n">
-        <v>55.8</v>
+        <v>26.5</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -6749,119 +6753,113 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G108" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Miletus (IRE)</t>
+          <t>The Cutest (IRE)</t>
         </is>
       </c>
       <c r="I108" t="n">
         <v>5</v>
       </c>
       <c r="J108" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="K108" t="n">
-        <v>82</v>
-      </c>
-      <c r="L108" t="n">
-        <v>3.05</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
-        <v>83.14</v>
-      </c>
-      <c r="N108" t="n">
-        <v>61.4</v>
-      </c>
+        <v>88.88</v>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C109" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G109" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Documenting</t>
+          <t>Bad Habits (IRE)</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K109" t="n">
-        <v>77</v>
-      </c>
-      <c r="L109" t="n">
-        <v>3.2</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>83.14</v>
+        <v>88.88</v>
       </c>
       <c r="N109" t="n">
-        <v>54.7</v>
+        <v>59.3</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6869,59 +6867,59 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C110" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Gorgeous Mr George (IRE)</t>
+          <t>So Chic (IRE)</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K110" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="L110" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="M110" t="n">
-        <v>83.14</v>
+        <v>88.88</v>
       </c>
       <c r="N110" t="n">
-        <v>56.5</v>
+        <v>54.1</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -6929,59 +6927,59 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G111" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Grabajabba</t>
+          <t>Gundogan</t>
         </is>
       </c>
       <c r="I111" t="n">
         <v>5</v>
       </c>
       <c r="J111" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K111" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L111" t="n">
-        <v>3.85</v>
+        <v>1.75</v>
       </c>
       <c r="M111" t="n">
-        <v>83.14</v>
+        <v>88.88</v>
       </c>
       <c r="N111" t="n">
-        <v>53.7</v>
+        <v>53.3</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -6989,59 +6987,59 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Man Of Desert</t>
+          <t>Ravenglass (IRE)</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K112" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="L112" t="n">
-        <v>4.85</v>
+        <v>1.85</v>
       </c>
       <c r="M112" t="n">
-        <v>83.14</v>
+        <v>88.88</v>
       </c>
       <c r="N112" t="n">
-        <v>50.4</v>
+        <v>55.2</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -7049,59 +7047,59 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113" t="n">
-        <v>7.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G113" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Captain Parma (IRE)</t>
+          <t>Street Dancer (IRE)</t>
         </is>
       </c>
       <c r="I113" t="n">
         <v>4</v>
       </c>
       <c r="J113" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K113" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L113" t="n">
-        <v>4.95</v>
+        <v>2.35</v>
       </c>
       <c r="M113" t="n">
-        <v>83.14</v>
+        <v>88.88</v>
       </c>
       <c r="N113" t="n">
-        <v>52.7</v>
+        <v>45.9</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -7109,113 +7107,119 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>7</v>
       </c>
       <c r="C114" t="n">
-        <v>8.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>6</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Serragasso</t>
+          <t>Ashford Hill</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K114" t="n">
-        <v>52</v>
-      </c>
-      <c r="L114" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="L114" t="n">
+        <v>3.6</v>
+      </c>
       <c r="M114" t="n">
-        <v>96.88</v>
-      </c>
-      <c r="N114" t="inlineStr"/>
+        <v>88.88</v>
+      </c>
+      <c r="N114" t="n">
+        <v>42.8</v>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>7</v>
       </c>
       <c r="C115" t="n">
-        <v>8.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F115" t="n">
         <v>6</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Lucky Sevens</t>
+          <t>Top Star (IRE)</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K115" t="n">
-        <v>46</v>
-      </c>
-      <c r="L115" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="L115" t="n">
+        <v>6.1</v>
+      </c>
       <c r="M115" t="n">
-        <v>96.88</v>
+        <v>88.88</v>
       </c>
       <c r="N115" t="n">
-        <v>64.3</v>
+        <v>38.7</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -7223,59 +7227,59 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>7</v>
       </c>
       <c r="C116" t="n">
-        <v>8.013636363636364</v>
+        <v>7.163636363636364</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>6</v>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Very Demure</t>
+          <t>Big Gypsy King</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K116" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L116" t="n">
-        <v>1</v>
+        <v>8.85</v>
       </c>
       <c r="M116" t="n">
-        <v>96.88</v>
+        <v>88.88</v>
       </c>
       <c r="N116" t="n">
-        <v>65</v>
+        <v>30.8</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -7283,59 +7287,57 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C117" t="n">
-        <v>8.013636363636364</v>
+        <v>9.472727272727273</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F117" t="n">
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Lady Of Clover (IRE)</t>
+          <t>Kaaranah (IRE)</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K117" t="n">
-        <v>49</v>
-      </c>
-      <c r="L117" t="n">
-        <v>1.1</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>96.88</v>
+        <v>124.79</v>
       </c>
       <c r="N117" t="n">
-        <v>62.7</v>
+        <v>9.6</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -7349,53 +7351,53 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C118" t="n">
-        <v>8.013636363636364</v>
+        <v>9.472727272727273</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F118" t="n">
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Poetic Grace (IRE)</t>
+          <t>Karakula</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K118" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="L118" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="M118" t="n">
-        <v>96.88</v>
+        <v>124.79</v>
       </c>
       <c r="N118" t="n">
-        <v>58.8</v>
+        <v>-9</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -7403,59 +7405,59 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C119" t="n">
-        <v>8.013636363636364</v>
+        <v>9.472727272727273</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Shes Crafty (IRE)</t>
+          <t>Eagles Whistle (IRE)</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J119" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K119" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L119" t="n">
-        <v>5.35</v>
+        <v>4.25</v>
       </c>
       <c r="M119" t="n">
-        <v>96.88</v>
+        <v>124.79</v>
       </c>
       <c r="N119" t="n">
-        <v>56.4</v>
+        <v>-9</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -7463,59 +7465,59 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C120" t="n">
-        <v>8.013636363636364</v>
+        <v>9.472727272727273</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F120" t="n">
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Akrivos (IRE)</t>
+          <t>Moonlit Cloud</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J120" t="n">
         <v>128</v>
       </c>
       <c r="K120" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L120" t="n">
-        <v>11.35</v>
+        <v>6.25</v>
       </c>
       <c r="M120" t="n">
-        <v>96.88</v>
+        <v>124.79</v>
       </c>
       <c r="N120" t="n">
-        <v>35.8</v>
+        <v>-19.7</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -7529,53 +7531,53 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C121" t="n">
-        <v>8.013636363636364</v>
+        <v>9.472727272727273</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>6</v>
       </c>
       <c r="G121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Three Builders (IRE)</t>
+          <t>Nuptown Girl</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K121" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L121" t="n">
-        <v>19.35</v>
+        <v>9.5</v>
       </c>
       <c r="M121" t="n">
-        <v>96.88</v>
+        <v>124.79</v>
       </c>
       <c r="N121" t="n">
-        <v>23</v>
+        <v>-22.5</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -7583,67 +7585,67 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>YARMOUTH</t>
+          <t>WOLVERHAMPTON</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C122" t="n">
-        <v>8.013636363636364</v>
+        <v>9.472727272727273</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Good To Firm</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Turf</t>
+          <t>All Weather</t>
         </is>
       </c>
       <c r="F122" t="n">
         <v>6</v>
       </c>
       <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Distinction (IRE)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
         <v>8</v>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Ibiza Lights (IRE)</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>3</v>
-      </c>
       <c r="J122" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K122" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="L122" t="n">
-        <v>20.35</v>
+        <v>10.5</v>
       </c>
       <c r="M122" t="n">
-        <v>96.88</v>
+        <v>124.79</v>
       </c>
       <c r="N122" t="n">
-        <v>29.6</v>
+        <v>-28</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7653,56 +7655,3386 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Siouxperb</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" t="n">
+        <v>133</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="N123" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ogorman</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>133</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>4</v>
+      </c>
+      <c r="M124" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="N124" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Priscillas Hope</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>2</v>
+      </c>
+      <c r="J125" t="n">
+        <v>128</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
         <v>7</v>
       </c>
-      <c r="C123" t="n">
+      <c r="M125" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="N125" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Viking Barbie (IRE)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>2</v>
+      </c>
+      <c r="J126" t="n">
+        <v>128</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M126" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="N126" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Hamdani Mokhater</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>133</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="M127" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="N127" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Taseem</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>133</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="M128" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="N128" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="n">
+        <v>11.47272727272727</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>4</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Close To Me</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>138</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" t="n">
+        <v>11.47272727272727</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Brilliant Star</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>123</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="N130" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" t="n">
+        <v>11.47272727272727</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>4</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Fanciulla Del West</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>121</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>10</v>
+      </c>
+      <c r="M131" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="N131" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" t="n">
+        <v>11.47272727272727</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>4</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kenkelly (IRE)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>123</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M132" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="N132" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" t="n">
+        <v>11.47272727272727</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" t="n">
+        <v>4</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Clarissa Eclipse</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>3</v>
+      </c>
+      <c r="J133" t="n">
+        <v>121</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M133" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="N133" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="n">
+        <v>11.47272727272727</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>4</v>
+      </c>
+      <c r="G134" t="n">
+        <v>5</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Millies A Minx</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>140</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="M134" t="n">
+        <v>141.08</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Room Fourteen</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>3</v>
+      </c>
+      <c r="J135" t="n">
+        <v>131</v>
+      </c>
+      <c r="K135" t="n">
+        <v>66</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N135" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>5</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>King Of Berkshire (IRE)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>3</v>
+      </c>
+      <c r="J136" t="n">
+        <v>134</v>
+      </c>
+      <c r="K136" t="n">
+        <v>69</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N136" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>3</v>
+      </c>
+      <c r="C137" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Crimson Rambler</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>3</v>
+      </c>
+      <c r="J137" t="n">
+        <v>135</v>
+      </c>
+      <c r="K137" t="n">
+        <v>70</v>
+      </c>
+      <c r="L137" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M137" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N137" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Boilermaker (FR)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>3</v>
+      </c>
+      <c r="J138" t="n">
+        <v>128</v>
+      </c>
+      <c r="K138" t="n">
+        <v>63</v>
+      </c>
+      <c r="L138" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M138" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N138" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>5</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Heated Moment</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>121</v>
+      </c>
+      <c r="K139" t="n">
+        <v>56</v>
+      </c>
+      <c r="L139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M139" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N139" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Joyful Lawyer (USA)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>3</v>
+      </c>
+      <c r="J140" t="n">
+        <v>132</v>
+      </c>
+      <c r="K140" t="n">
+        <v>67</v>
+      </c>
+      <c r="L140" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M140" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N140" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>3</v>
+      </c>
+      <c r="C141" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>5</v>
+      </c>
+      <c r="G141" t="n">
+        <v>7</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kokushoku (IRE)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>3</v>
+      </c>
+      <c r="J141" t="n">
+        <v>131</v>
+      </c>
+      <c r="K141" t="n">
+        <v>66</v>
+      </c>
+      <c r="L141" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="M141" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N141" t="n">
+        <v>61</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>5</v>
+      </c>
+      <c r="G142" t="n">
+        <v>8</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Pantiles Gift</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>3</v>
+      </c>
+      <c r="J142" t="n">
+        <v>136</v>
+      </c>
+      <c r="K142" t="n">
+        <v>71</v>
+      </c>
+      <c r="L142" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="M142" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N142" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>3</v>
+      </c>
+      <c r="C143" t="n">
+        <v>10.10454545454546</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>9</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Izznt She Hot</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>3</v>
+      </c>
+      <c r="J143" t="n">
+        <v>132</v>
+      </c>
+      <c r="K143" t="n">
+        <v>67</v>
+      </c>
+      <c r="L143" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="M143" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="N143" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>4</v>
+      </c>
+      <c r="C144" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Caragio (IRE)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>6</v>
+      </c>
+      <c r="J144" t="n">
+        <v>131</v>
+      </c>
+      <c r="K144" t="n">
+        <v>66</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="N144" t="n">
+        <v>74</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>5</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Dark Side Thunder</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>7</v>
+      </c>
+      <c r="J145" t="n">
+        <v>134</v>
+      </c>
+      <c r="K145" t="n">
+        <v>69</v>
+      </c>
+      <c r="L145" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M145" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="N145" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>4</v>
+      </c>
+      <c r="C146" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Fenlander</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>5</v>
+      </c>
+      <c r="J146" t="n">
+        <v>126</v>
+      </c>
+      <c r="K146" t="n">
+        <v>61</v>
+      </c>
+      <c r="L146" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M146" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="N146" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>4</v>
+      </c>
+      <c r="C147" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>4</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Ironist (IRE)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>4</v>
+      </c>
+      <c r="J147" t="n">
+        <v>135</v>
+      </c>
+      <c r="K147" t="n">
+        <v>70</v>
+      </c>
+      <c r="L147" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M147" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="N147" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>My Mate Kev</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>4</v>
+      </c>
+      <c r="J148" t="n">
+        <v>128</v>
+      </c>
+      <c r="K148" t="n">
+        <v>63</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M148" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="N148" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>5</v>
+      </c>
+      <c r="G149" t="n">
+        <v>6</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bill Plumb (IRE)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>134</v>
+      </c>
+      <c r="K149" t="n">
+        <v>69</v>
+      </c>
+      <c r="L149" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="M149" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="N149" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>5</v>
+      </c>
+      <c r="C150" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>5</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Love Alive</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>3</v>
+      </c>
+      <c r="J150" t="n">
+        <v>133</v>
+      </c>
+      <c r="K150" t="n">
+        <v>68</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Space Bear (IRE)</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>3</v>
+      </c>
+      <c r="J151" t="n">
+        <v>135</v>
+      </c>
+      <c r="K151" t="n">
+        <v>70</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N151" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Argy Bhaji</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>132</v>
+      </c>
+      <c r="K152" t="n">
+        <v>67</v>
+      </c>
+      <c r="L152" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M152" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N152" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>5</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Eightthreeone</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>3</v>
+      </c>
+      <c r="J153" t="n">
+        <v>133</v>
+      </c>
+      <c r="K153" t="n">
+        <v>68</v>
+      </c>
+      <c r="L153" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M153" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N153" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>5</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ocean Of Storms (FR)</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" t="n">
+        <v>132</v>
+      </c>
+      <c r="K154" t="n">
+        <v>67</v>
+      </c>
+      <c r="L154" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M154" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N154" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>5</v>
+      </c>
+      <c r="G155" t="n">
+        <v>5</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Eyes Front (IRE)</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" t="n">
+        <v>134</v>
+      </c>
+      <c r="K155" t="n">
+        <v>69</v>
+      </c>
+      <c r="L155" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M155" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N155" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>5</v>
+      </c>
+      <c r="G156" t="n">
+        <v>6</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Angel Summer (IRE)</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" t="n">
+        <v>127</v>
+      </c>
+      <c r="K156" t="n">
+        <v>62</v>
+      </c>
+      <c r="L156" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M156" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N156" t="n">
+        <v>42</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" t="n">
+        <v>6.013636363636364</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>7</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Wild Rosie</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" t="n">
+        <v>129</v>
+      </c>
+      <c r="K157" t="n">
+        <v>64</v>
+      </c>
+      <c r="L157" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M157" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="N157" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>6</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>4</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Dashing Dick (IRE)</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>8</v>
+      </c>
+      <c r="J158" t="n">
+        <v>133</v>
+      </c>
+      <c r="K158" t="n">
+        <v>78</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>6</v>
+      </c>
+      <c r="C159" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>4</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>4</v>
+      </c>
+      <c r="J159" t="n">
+        <v>137</v>
+      </c>
+      <c r="K159" t="n">
+        <v>82</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N159" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>6</v>
+      </c>
+      <c r="C160" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>4</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Candonomore (FR)</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>132</v>
+      </c>
+      <c r="K160" t="n">
+        <v>77</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M160" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N160" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>6</v>
+      </c>
+      <c r="C161" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>4</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Rogue Allegiance (IRE)</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>4</v>
+      </c>
+      <c r="J161" t="n">
+        <v>126</v>
+      </c>
+      <c r="K161" t="n">
+        <v>71</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M161" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N161" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>6</v>
+      </c>
+      <c r="C162" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>4</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Shimmering Spin (USA)</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>5</v>
+      </c>
+      <c r="J162" t="n">
+        <v>129</v>
+      </c>
+      <c r="K162" t="n">
+        <v>74</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M162" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N162" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>4</v>
+      </c>
+      <c r="G163" t="n">
+        <v>5</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Mister Mojito (IRE)</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>5</v>
+      </c>
+      <c r="J163" t="n">
+        <v>127</v>
+      </c>
+      <c r="K163" t="n">
+        <v>72</v>
+      </c>
+      <c r="L163" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M163" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N163" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>6</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>4</v>
+      </c>
+      <c r="G164" t="n">
+        <v>6</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Miletus (IRE)</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>137</v>
+      </c>
+      <c r="K164" t="n">
+        <v>82</v>
+      </c>
+      <c r="L164" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M164" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N164" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>6</v>
+      </c>
+      <c r="C165" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>4</v>
+      </c>
+      <c r="G165" t="n">
+        <v>7</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Documenting</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>13</v>
+      </c>
+      <c r="J165" t="n">
+        <v>132</v>
+      </c>
+      <c r="K165" t="n">
+        <v>77</v>
+      </c>
+      <c r="L165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M165" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N165" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>6</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>8</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Gorgeous Mr George (IRE)</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>4</v>
+      </c>
+      <c r="J166" t="n">
+        <v>133</v>
+      </c>
+      <c r="K166" t="n">
+        <v>78</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M166" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N166" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>4</v>
+      </c>
+      <c r="G167" t="n">
+        <v>9</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Grabajabba</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>5</v>
+      </c>
+      <c r="J167" t="n">
+        <v>131</v>
+      </c>
+      <c r="K167" t="n">
+        <v>76</v>
+      </c>
+      <c r="L167" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="M167" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N167" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>4</v>
+      </c>
+      <c r="G168" t="n">
+        <v>10</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Man Of Desert</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>5</v>
+      </c>
+      <c r="J168" t="n">
+        <v>130</v>
+      </c>
+      <c r="K168" t="n">
+        <v>75</v>
+      </c>
+      <c r="L168" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="M168" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N168" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>6</v>
+      </c>
+      <c r="C169" t="n">
+        <v>7.013636363636364</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>4</v>
+      </c>
+      <c r="G169" t="n">
+        <v>11</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Captain Parma (IRE)</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>4</v>
+      </c>
+      <c r="J169" t="n">
+        <v>133</v>
+      </c>
+      <c r="K169" t="n">
+        <v>78</v>
+      </c>
+      <c r="L169" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M169" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="N169" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>7</v>
+      </c>
+      <c r="C170" t="n">
         <v>8.013636363636364</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>Good To Firm</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>6</v>
-      </c>
-      <c r="G123" t="n">
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>6</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Serragasso</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>3</v>
+      </c>
+      <c r="J170" t="n">
+        <v>132</v>
+      </c>
+      <c r="K170" t="n">
+        <v>52</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>7</v>
+      </c>
+      <c r="C171" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>6</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Lucky Sevens</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>3</v>
+      </c>
+      <c r="J171" t="n">
+        <v>126</v>
+      </c>
+      <c r="K171" t="n">
+        <v>46</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N171" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>7</v>
+      </c>
+      <c r="C172" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>6</v>
+      </c>
+      <c r="G172" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Very Demure</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>3</v>
+      </c>
+      <c r="J172" t="n">
+        <v>130</v>
+      </c>
+      <c r="K172" t="n">
+        <v>50</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N172" t="n">
+        <v>65</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>7</v>
+      </c>
+      <c r="C173" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>6</v>
+      </c>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Lady Of Clover (IRE)</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>3</v>
+      </c>
+      <c r="J173" t="n">
+        <v>129</v>
+      </c>
+      <c r="K173" t="n">
+        <v>49</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N173" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>7</v>
+      </c>
+      <c r="C174" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>6</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Poetic Grace (IRE)</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>3</v>
+      </c>
+      <c r="J174" t="n">
+        <v>126</v>
+      </c>
+      <c r="K174" t="n">
+        <v>46</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M174" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N174" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>6</v>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Shes Crafty (IRE)</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>3</v>
+      </c>
+      <c r="J175" t="n">
+        <v>135</v>
+      </c>
+      <c r="K175" t="n">
+        <v>55</v>
+      </c>
+      <c r="L175" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M175" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N175" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>7</v>
+      </c>
+      <c r="C176" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>6</v>
+      </c>
+      <c r="G176" t="n">
+        <v>6</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Akrivos (IRE)</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>3</v>
+      </c>
+      <c r="J176" t="n">
+        <v>128</v>
+      </c>
+      <c r="K176" t="n">
+        <v>48</v>
+      </c>
+      <c r="L176" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="M176" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N176" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>7</v>
+      </c>
+      <c r="C177" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>6</v>
+      </c>
+      <c r="G177" t="n">
+        <v>7</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Three Builders (IRE)</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>3</v>
+      </c>
+      <c r="J177" t="n">
+        <v>135</v>
+      </c>
+      <c r="K177" t="n">
+        <v>55</v>
+      </c>
+      <c r="L177" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="M177" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N177" t="n">
+        <v>23</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>6</v>
+      </c>
+      <c r="G178" t="n">
+        <v>8</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Ibiza Lights (IRE)</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>3</v>
+      </c>
+      <c r="J178" t="n">
+        <v>130</v>
+      </c>
+      <c r="K178" t="n">
+        <v>50</v>
+      </c>
+      <c r="L178" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="M178" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="N178" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>YARMOUTH</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>7</v>
+      </c>
+      <c r="C179" t="n">
+        <v>8.013636363636364</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Good To Firm</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Turf</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>6</v>
+      </c>
+      <c r="G179" t="n">
         <v>9</v>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>Regal And Real</t>
         </is>
       </c>
-      <c r="I123" t="n">
+      <c r="I179" t="n">
         <v>3</v>
       </c>
-      <c r="J123" t="n">
+      <c r="J179" t="n">
         <v>126</v>
       </c>
-      <c r="K123" t="n">
+      <c r="K179" t="n">
         <v>46</v>
       </c>
-      <c r="L123" t="n">
+      <c r="L179" t="n">
         <v>20.5</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M179" t="n">
         <v>96.88</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N179" t="n">
         <v>26.6</v>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O179" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P123" t="n">
+      <c r="P179" t="n">
         <v>1</v>
       </c>
     </row>
